--- a/docs/Ae3.xlsx
+++ b/docs/Ae3.xlsx
@@ -494,7 +494,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MES : 5 2026</t>
+          <t>MES : 11 2024</t>
         </is>
       </c>
     </row>
@@ -737,29 +737,45 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>165</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>803</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1054</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>435</v>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
@@ -807,17 +823,17 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
@@ -872,7 +888,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -903,7 +919,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -932,42 +948,44 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>63</v>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>98</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K17" s="7" t="n"/>
@@ -991,7 +1009,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -1022,7 +1040,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -1053,7 +1071,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
@@ -1084,7 +1102,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -1115,7 +1133,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D22" s="3" t="n"/>
@@ -1146,7 +1164,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -1177,7 +1195,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>448</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
@@ -1208,29 +1226,43 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>165</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>803</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>1054</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>435</v>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
@@ -1253,7 +1285,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="3" t="n"/>
@@ -1286,7 +1318,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Aprobado por: admin</t>
+          <t>Aprobado por: emanuel</t>
         </is>
       </c>
     </row>
